--- a/12605273.xlsx
+++ b/12605273.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B45900E2-3FBD-9F43-BF21-C4D35611B192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1D4F6CE-974C-644E-A65E-0414116CCCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -210,10 +210,46 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Example row — replace with your own data. Felt a bit tired after evening class.</t>
+    <t xml:space="preserve"> Attended 3 classes today;classes went well</t>
   </si>
   <si>
-    <t xml:space="preserve"> Attended 3 classes today;classes went well</t>
+    <t>Attended 4 lectures today;classes went well</t>
+  </si>
+  <si>
+    <t>Attended 8 lectures today;classes went well</t>
+  </si>
+  <si>
+    <t>No class today</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Attended 6 lectures today;classes went neutral</t>
+  </si>
+  <si>
+    <t>Attended 3 lectures today;classes went well</t>
+  </si>
+  <si>
+    <t>Attended 5 lectures today;classes went great</t>
+  </si>
+  <si>
+    <t>On leave</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -992,9 +1028,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="39.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="27" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="B6" s="9">
         <v>420</v>
@@ -1012,7 +1048,7 @@
         <v>180</v>
       </c>
       <c r="G6" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H6" s="9">
         <v>30</v>
@@ -1035,7 +1071,7 @@
         <v>55</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
@@ -1081,448 +1117,894 @@
         <v>55</v>
       </c>
       <c r="N7" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B8" s="14">
+        <v>540</v>
+      </c>
+      <c r="C8" s="14">
+        <v>40</v>
+      </c>
+      <c r="D8" s="14">
+        <v>150</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="1"/>
+        <v>390</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
-    </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B9" s="14">
+        <v>600</v>
+      </c>
+      <c r="C9" s="14">
+        <v>45</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="A10" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B10" s="14">
+        <v>540</v>
+      </c>
+      <c r="C10" s="14">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>90</v>
+      </c>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+        <v>590</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B11" s="14">
+        <v>480</v>
+      </c>
+      <c r="C11" s="14">
+        <v>45</v>
+      </c>
+      <c r="D11" s="14">
+        <v>90</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>6</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>375</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B12" s="14">
+        <v>480</v>
+      </c>
+      <c r="C12" s="14">
+        <v>40</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>150</v>
+      </c>
+      <c r="G12" s="14">
+        <v>3</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>90</v>
+      </c>
+      <c r="F13" s="14">
+        <v>250</v>
+      </c>
+      <c r="G13" s="14">
+        <v>5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>40</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
+      <c r="A14" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B14" s="14">
+        <v>600</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="A15" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B15" s="14">
+        <v>600</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>120</v>
+      </c>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="H15" s="14">
+        <v>40</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="A16" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540</v>
+      </c>
+      <c r="C16" s="14">
+        <v>40</v>
+      </c>
+      <c r="D16" s="14">
+        <v>120</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="A17" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B17" s="14">
+        <v>540</v>
+      </c>
+      <c r="C17" s="14">
+        <v>40</v>
+      </c>
+      <c r="D17" s="14">
+        <v>90</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="H17" s="14">
+        <v>150</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>45</v>
+      </c>
+      <c r="D18" s="14">
+        <v>120</v>
+      </c>
+      <c r="E18" s="14">
+        <v>90</v>
+      </c>
+      <c r="F18" s="14">
+        <v>300</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>345</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>90</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>150</v>
+      </c>
+      <c r="G19" s="14">
+        <v>3</v>
+      </c>
+      <c r="H19" s="14">
+        <v>40</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
+        <v>590</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
       <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>90</v>
+      </c>
+      <c r="F20" s="14">
+        <v>400</v>
+      </c>
+      <c r="G20" s="14">
+        <v>8</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>120</v>
+      </c>
+      <c r="F21" s="14">
+        <v>300</v>
+      </c>
+      <c r="G21" s="14">
+        <v>6</v>
+      </c>
+      <c r="H21" s="14">
+        <v>40</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>440</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>45</v>
+      </c>
+      <c r="D22" s="14">
+        <v>120</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>40</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>995</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>445</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="A23" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B23" s="14">
+        <v>540</v>
+      </c>
+      <c r="C23" s="14">
+        <v>50</v>
+      </c>
+      <c r="D23" s="14">
+        <v>90</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="H23" s="14">
+        <v>50</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="A24" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B24" s="14">
+        <v>600</v>
+      </c>
+      <c r="C24" s="14">
+        <v>40</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>90</v>
+      </c>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>40</v>
+      </c>
+      <c r="D25" s="14">
+        <v>90</v>
+      </c>
+      <c r="E25" s="14">
+        <v>90</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>440</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B26" s="14">
+        <v>540</v>
+      </c>
+      <c r="C26" s="14">
+        <v>40</v>
+      </c>
+      <c r="D26">
+        <v>180</v>
+      </c>
+      <c r="E26" s="14">
+        <v>90</v>
+      </c>
+      <c r="F26" s="14">
+        <v>150</v>
+      </c>
+      <c r="G26" s="14">
+        <v>3</v>
+      </c>
+      <c r="H26" s="14">
+        <v>30</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>410</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B27" s="14">
+        <v>450</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>90</v>
+      </c>
+      <c r="E27" s="14">
+        <v>90</v>
+      </c>
+      <c r="F27" s="14">
+        <v>400</v>
+      </c>
+      <c r="G27" s="14">
+        <v>8</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>

--- a/12605273.xlsx
+++ b/12605273.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1D4F6CE-974C-644E-A65E-0414116CCCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{96295C39-F2F4-854F-BF08-FE534EC7909F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2006,137 +2006,267 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B28" s="14">
+        <v>490</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>90</v>
+      </c>
+      <c r="E28" s="14">
+        <v>90</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B29" s="14">
+        <v>540</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>90</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>90</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="A30" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B30" s="14">
+        <v>540</v>
+      </c>
+      <c r="C30" s="14">
+        <v>45</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>120</v>
+      </c>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="A31" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B31" s="14">
+        <v>540</v>
+      </c>
+      <c r="C31" s="14">
+        <v>45</v>
+      </c>
+      <c r="D31" s="14">
+        <v>150</v>
+      </c>
+      <c r="E31" s="14">
+        <v>120</v>
+      </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="H31" s="14">
+        <v>90</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>495</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B32" s="14">
+        <v>540</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>90</v>
+      </c>
+      <c r="F32" s="14">
+        <v>400</v>
+      </c>
+      <c r="G32" s="14">
+        <v>8</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>200</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
+      <c r="A33" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B33" s="14">
+        <v>540</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>150</v>
+      </c>
+      <c r="E33" s="14">
+        <v>90</v>
+      </c>
       <c r="F33" s="14"/>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
